--- a/docs/DB_스키마.xlsx
+++ b/docs/DB_스키마.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -217,6 +217,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,13 +588,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -626,6 +633,11 @@
           <t>사용방법</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>담당자 (R&amp;R)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -648,6 +660,11 @@
         <is>
           <t>회원가입·로그인 인증
 반려동물·게시글·댓글의 기준 테이블</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
         </is>
       </c>
     </row>
@@ -670,6 +687,11 @@
 관리자/수의사 기능 구분</t>
         </is>
       </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="n"/>
@@ -690,6 +712,11 @@
 OAuth2 Provider별 고유 ID 연동</t>
         </is>
       </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="7" t="n"/>
@@ -708,6 +735,11 @@
           <t>회원가입 시 이용약관, 개인정보, 마케팅 동의 저장</t>
         </is>
       </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="n"/>
@@ -726,6 +758,11 @@
           <t>Access Token 재발급 및 세션 조작 방지 (Token Rotation)</t>
         </is>
       </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="8" t="n"/>
@@ -744,6 +781,11 @@
           <t>AI 진단 완료, 경과 관찰 주기 알림, 24시 응급 경고 푸시 알림</t>
         </is>
       </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -765,6 +807,11 @@
       <c r="D11" s="11" t="inlineStr">
         <is>
           <t>반려동물 온보딩, AI 진단 및 타임라인 경과 비교의 기준 테이블</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
         </is>
       </c>
     </row>
@@ -786,6 +833,11 @@
           <t>반려동물 등록 시 선택 가능한 축종 마스터 정보</t>
         </is>
       </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="n"/>
@@ -804,6 +856,11 @@
           <t>반려동물 등록 시 품종 드롭다운 자동완성 마스터 데이터</t>
         </is>
       </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="7" t="n"/>
@@ -822,6 +879,11 @@
           <t>알레르기, 기저질환, 중성화 여부, 수술 이력, 예방접종 이력 관리</t>
         </is>
       </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n"/>
@@ -840,6 +902,11 @@
           <t>시간 경과에 따른 체중 변화 기록 및 체중 변화 그래프 렌더링</t>
         </is>
       </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>👤 태준 (User)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -860,6 +927,11 @@
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>환부 사진 업로드, 의심 질환 Top 3, 위험도 레벨(관찰/주의 vs 응급) 판정</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
         </is>
       </c>
     </row>
@@ -880,6 +952,11 @@
           <t>진단 이미지 원본 URL, 썸네일 URL, Vision AI 바운딩 박스 좌표</t>
         </is>
       </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="7" t="n"/>
@@ -898,6 +975,11 @@
           <t>피부, 안구, 귀, 구강, 관절/지체 등 환부 분류 마스터</t>
         </is>
       </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="n"/>
@@ -916,6 +998,11 @@
           <t>AI 진단 입력 폼에서 환부별 체크박스 리스트 동적 제공 마스터 테이블</t>
         </is>
       </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="7" t="n"/>
@@ -934,6 +1021,11 @@
           <t>질환명, 원인, 증상, 임상가이드 (ChromaDB Vector DB 백업용)</t>
         </is>
       </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="8" t="n"/>
@@ -952,6 +1044,11 @@
           <t>Vision AI 가 학습한 질환 코드, 분류명, 위험도 기본값 마스터</t>
         </is>
       </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -972,6 +1069,11 @@
       <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Before/After 이미지 슬라이더 비교 및 Gemini AI 경과 변화 추이 분석</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
         </is>
       </c>
     </row>
@@ -992,6 +1094,11 @@
           <t>AI 경과 소견에 대한 실제 호전 여부 유저 피드백 및 수의사 검토 소견</t>
         </is>
       </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="8" t="n"/>
@@ -1010,6 +1117,11 @@
           <t>경과 관찰 재진단 유도 푸시 알림 예약 및 발송 여부</t>
         </is>
       </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>🤖 진한님</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1030,6 +1142,11 @@
       <c r="D25" s="6" t="inlineStr">
         <is>
           <t>카카오/네이버 지도 API 연동, 위험도 EMERGENCY 시 24시 응급 병원 핫링크</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>🏥 지호님</t>
         </is>
       </c>
     </row>
@@ -1050,6 +1167,11 @@
           <t>병원 요일별 진료 시간 및 야간 24시 응급 진료 시간 명세</t>
         </is>
       </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>🏥 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="7" t="n"/>
@@ -1069,6 +1191,11 @@
           <t>동물병원 전문 진료 과목 및 24시 응급센터 여부</t>
         </is>
       </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>🏥 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="8" t="n"/>
@@ -1088,6 +1215,11 @@
           <t>자주 가는 동물병원 북마크 등록 및 마이페이지 조회</t>
         </is>
       </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>🏥 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -1108,6 +1240,11 @@
       <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Spring Boot @Scheduled(cron='0 0 */6 * * *')로 6시간 주기 자동 캐싱</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
         </is>
       </c>
     </row>
@@ -1128,6 +1265,11 @@
           <t>건강/질병, 사료/리콜, 일반 펫 뉴스 카테고리 분류 마스터</t>
         </is>
       </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>📰 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -1148,6 +1290,11 @@
       <c r="D31" s="6" t="inlineStr">
         <is>
           <t>비슷한 증상을 겪은 반려인 간 질문/노하우 정보 공유 (선택적 소셜)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>💬 지호님</t>
         </is>
       </c>
     </row>
@@ -1168,6 +1315,11 @@
           <t>게시글 작성 시 수동 첨부하는 사진 파일 리스트</t>
         </is>
       </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>💬 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="7" t="n"/>
@@ -1186,6 +1338,11 @@
           <t>게시글 1:N 댓글 작성 및 부모 댓글(parent_id) 대댓글 소통</t>
         </is>
       </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>💬 지호님</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="8" t="n"/>
@@ -1202,6 +1359,11 @@
       <c r="D34" s="6" t="inlineStr">
         <is>
           <t>게시글 추천 중복 방지 및 좋아요 수 집계</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>💬 지호님</t>
         </is>
       </c>
     </row>
